--- a/outputs/model_results/MCLR/Model 2_seuils.xlsx
+++ b/outputs/model_results/MCLR/Model 2_seuils.xlsx
@@ -471,12 +471,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,14 +486,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1850</v>
+        <v>4975</v>
       </c>
       <c r="G2" t="n">
-        <v>2108</v>
+        <v>2786</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -502,12 +502,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0065</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0071</t>
+          <t>0.0047</t>
         </is>
       </c>
     </row>
@@ -519,12 +519,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -534,14 +534,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1917</v>
+        <v>4850</v>
       </c>
       <c r="G3" t="n">
-        <v>2137</v>
+        <v>2638</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -550,12 +550,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0065</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0069</t>
+          <t>0.0047</t>
         </is>
       </c>
     </row>
@@ -567,29 +567,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.0012</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1936</v>
+        <v>4899</v>
       </c>
       <c r="G4" t="n">
-        <v>2005</v>
+        <v>2518</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -598,12 +598,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0099</t>
+          <t>0.0065</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0069</t>
+          <t>0.0047</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -630,14 +630,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1991</v>
+        <v>4927</v>
       </c>
       <c r="G5" t="n">
-        <v>2058</v>
+        <v>2693</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -646,12 +646,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0098</t>
+          <t>0.0065</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0069</t>
+          <t>0.0047</t>
         </is>
       </c>
     </row>

--- a/outputs/model_results/MCLR/Model 2_seuils.xlsx
+++ b/outputs/model_results/MCLR/Model 2_seuils.xlsx
@@ -471,12 +471,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.462</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,14 +486,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4975</v>
+        <v>6301</v>
       </c>
       <c r="G2" t="n">
-        <v>2786</v>
+        <v>3132</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -502,12 +502,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0065</t>
+          <t>0.0058</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0047</t>
+          <t>0.004</t>
         </is>
       </c>
     </row>
@@ -519,12 +519,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4850</v>
+        <v>6216</v>
       </c>
       <c r="G3" t="n">
-        <v>2638</v>
+        <v>3084</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -550,12 +550,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0065</t>
+          <t>0.0058</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0047</t>
+          <t>0.004</t>
         </is>
       </c>
     </row>
@@ -567,29 +567,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.0012</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4899</v>
+        <v>6132</v>
       </c>
       <c r="G4" t="n">
-        <v>2518</v>
+        <v>3173</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -598,12 +598,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0065</t>
+          <t>0.0059</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0047</t>
+          <t>0.0041</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.462</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4927</v>
+        <v>5935</v>
       </c>
       <c r="G5" t="n">
-        <v>2693</v>
+        <v>3013</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -646,12 +646,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0065</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0047</t>
+          <t>0.0042</t>
         </is>
       </c>
     </row>

--- a/outputs/model_results/MCLR/Model 2_seuils.xlsx
+++ b/outputs/model_results/MCLR/Model 2_seuils.xlsx
@@ -471,29 +471,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6301</v>
+        <v>3275</v>
       </c>
       <c r="G2" t="n">
-        <v>3132</v>
+        <v>2844</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -502,12 +502,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0058</t>
+          <t>0.0068</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.0048</t>
         </is>
       </c>
     </row>
@@ -519,12 +519,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -534,14 +534,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6216</v>
+        <v>3287</v>
       </c>
       <c r="G3" t="n">
-        <v>3084</v>
+        <v>2725</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -550,12 +550,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0058</t>
+          <t>0.0067</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.0048</t>
         </is>
       </c>
     </row>
@@ -567,29 +567,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.386</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6132</v>
+        <v>3272</v>
       </c>
       <c r="G4" t="n">
-        <v>3173</v>
+        <v>2733</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -598,12 +598,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0059</t>
+          <t>0.0067</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0041</t>
+          <t>0.0048</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -630,14 +630,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5935</v>
+        <v>3299</v>
       </c>
       <c r="G5" t="n">
-        <v>3013</v>
+        <v>2736</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -646,12 +646,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.0067</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0042</t>
+          <t>0.0048</t>
         </is>
       </c>
     </row>
